--- a/data/reports/report-2026-08-30.xlsx
+++ b/data/reports/report-2026-08-30.xlsx
@@ -16,9 +16,10 @@
     <sheet name="ファネル30日" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="日次推移" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="本日の判定" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="本日0830途中" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="CVR推移" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="曜日指数" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="予算見直しチェック" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="本日0830途中" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="CVR推移" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="曜日指数" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -641,7 +642,7 @@
         <v>89461</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K7" s="4" t="n">
         <v>0.133</v>
@@ -693,7 +694,7 @@
         <v>27786</v>
       </c>
       <c r="J8" s="6" t="n">
-        <v>0.699</v>
+        <v>0.999</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0.202</v>
@@ -745,7 +746,7 @@
         <v>42049</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>0.723</v>
+        <v>0.977</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>0.629</v>
@@ -757,12 +758,12 @@
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>✅維持</t>
+          <t>🚀伸ばす候補</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>⏸窓が割れた→据え置き</t>
+          <t>🚀3窓すべて目標超＋消化95%→+25%</t>
         </is>
       </c>
     </row>
@@ -797,7 +798,7 @@
         <v>9562</v>
       </c>
       <c r="J10" s="6" t="n">
-        <v>0.666</v>
+        <v>0.978</v>
       </c>
       <c r="K10" s="4" t="n">
         <v>0.137</v>
@@ -849,7 +850,7 @@
         <v>-9540</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>0.699</v>
+        <v>0.999</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>0.003</v>
@@ -901,7 +902,7 @@
         <v>25428</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="K12" s="4" t="n">
         <v>0.188</v>
@@ -1003,7 +1004,7 @@
         <v>6583</v>
       </c>
       <c r="J14" s="6" t="n">
-        <v>0.765</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>0.183</v>
@@ -1055,7 +1056,7 @@
         <v>29</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>0.697</v>
+        <v>0.996</v>
       </c>
       <c r="K15" s="4" t="n">
         <v>0.025</v>
@@ -1107,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="6" t="n">
-        <v>0.618</v>
+        <v>1.043</v>
       </c>
       <c r="K16" s="8" t="n">
         <v>-0.11</v>
@@ -1422,6 +1423,925 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="7" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-30 昼にユーザーが日予算を見直した。**変更後の値はMetaを直読して確認済み**（campaign_and_resource_get / campaign_detail_level="ad_groups"・ENABLEDの広告セットのみ合計）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>合計 253,000 → **255,000円**（+2,000円/日・+0.8%）。実質は「効率の良い3つへ +8,000／薄い3つから −6,000」の付け替え</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>★増額 3件: 快適マジックインソール +3,000(+11.1%) ／ むくみ取りかっさ +3,000(+30.0%) ／ バランスケアスリッパ +2,000(+20.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>★減額 3件: 2WAYシートボックス −2,000(−15.4%) ／ 完全遮光・接触冷感UVハット −2,000(−25.0%) ／ 偏光・調光サングラス −2,000(−28.6%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>★総評: **方向は正しい**。増額した3つは7日余裕が +0.94〜+1.62 と全商品の上位、減額した3つは3日余裕が +0.04〜+0.57 と縮んでいる側</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>⚠️ 週消化率はこのシートから計算方法を直した。同じ日に複数回スナップショットを取った日(8/23-25)を従来は合算しており、消化率が実態より低く出ていた。修正後、快適マジックインソールは 85%→**97.7%** になり、3窓判定が「据え置き」→「🚀3窓すべて目標超＋消化95%→+25%」に変わった</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>商品/キャンペーン</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>変更前</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>変更後</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>差</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>変化率</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>7日MER</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>分岐</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>目標</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>7日余裕</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>3日MER</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>3日余裕</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>倍率7日</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>倍率3日</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>消化率(7日)</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>1円あたり利益</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>頑健性</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>印</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>快適マジックインソール</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>27000</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0.1111111111111112</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="O9" s="4" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>むくみ取りかっさ</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M10" s="4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>1.021</v>
+      </c>
+      <c r="O10" s="4" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>バランスケアスリッパ</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="G11" s="4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J11" s="4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M11" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0.183</v>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>2WAYシートボックス</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>11000</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E12" s="13" t="n">
+        <v>-0.1538461538461539</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="G12" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>4.11</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="J12" s="4" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="M12" s="4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="O12" s="4" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>完全遮光・接触冷感UVハット</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>6000</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E13" s="13" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="G13" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J13" s="4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="M13" s="4" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>0.996</v>
+      </c>
+      <c r="O13" s="4" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>偏光・調光サングラス</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>7000</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E14" s="13" t="n">
+        <v>-0.2857142857142857</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M14" s="4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>★変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>ナノガラス脱毛パッド</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>80000</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="G15" s="4" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J15" s="4" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O15" s="4" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>W固定スマホ車載ホルダー</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>35000</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="G16" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="J16" s="4" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="K16" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L16" s="4" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="M16" s="4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="O16" s="4" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>カタログ全部（テスト）</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>18000</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ムダ毛シェーバー</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G18" s="4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>4.07</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J18" s="4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K18" s="4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="L18" s="4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="M18" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>0.978</v>
+      </c>
+      <c r="O18" s="4" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>姿勢サポートチェア</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="G19" s="4" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J19" s="4" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K19" s="4" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L19" s="4" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M19" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O19" s="4" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>ビジュアル耳かき</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="G20" s="4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J20" s="4" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="K20" s="4" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="L20" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M20" s="4" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>-0.193</v>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>ナノバブルシャワーヘッド</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="G21" s="4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H21" s="4" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J21" s="4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K21" s="4" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L21" s="4" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M21" s="4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>⚠️符号が割れる</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1702,7 +2622,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2374,7 +3294,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2508,7 +3428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2690,44 +3610,44 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>⏸ 前倒ししない</t>
+          <t>🔵 予算見直し</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>快適マジックインソール（3窓すべて目標超え）</t>
+          <t>8/30 昼にユーザーが6セット変更（合計 253,000→255,000円）</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>3窓とも MER 2.45〜2.83 で目標2.13を超えている。ただし 8/27に22,000→27,000へ増額済みで、**8/31の増額判定（P2=8/28-30の1日あたり利益 ≥ 28,310円）を宣言済み**。重ねての増額はしない。⚠️ P2は8/28-29の2日で1日あたり23,280円と基準を下回っており、8/30の出来次第。本日12:00時点の実売は7,960円と極端に低く、要監視</t>
+          <t>増額: 快適マジックインソール +3,000(+11.1%) ／ むくみ取りかっさ +3,000(+30.0%) ／ バランスケアスリッパ +2,000(+20.0%)。減額: 2WAY −2,000(−15.4%) ／ UVハット −2,000(−25.0%) ／ サングラス −2,000(−28.6%)。**方向は正しい**（増額側は7日余裕+0.94〜+1.62、減額側は3日余裕+0.04〜+0.57）。詳細は「予算見直しチェック」シート</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>週+1,143円見込み</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>8/31に執行</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 在庫</t>
+          <t>🚫 判定が壊れた</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>快適マジックインソール「グリーン」全7サイズが在庫0</t>
+          <t>快適マジックインソールの8/31判定は執行不能</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>他3色は各1万個以上ある。売れ筋色が買えない状態なので、非表示にするか色の選択肢から落とすかを決める。8/31の増額判定に直接効く</t>
+          <t>P2窓(8/28-30)の最終日に予算が27,000→30,000へ変わったため、宣言済みの判定は成立しない。「同一キャンペーンの再変更は前の実験を消費する」ルールに従い実験を終了し、**新しい実験（P1=8/28-29の27,000 vs P2=8/31-9/2の30,000・判定日9/3・合格ライン 1日23,280円）**を本日宣言する。⚠️ 予算は判定日の翌日以降に動かすと、この取りこぼしが起きない</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -2737,51 +3657,51 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>本日</t>
+          <t>9/3に執行</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>✅ 実行済み</t>
+          <t>⚠️ 学習中</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>3D足臭リセットブラシ 停止</t>
+          <t>むくみ取りかっさ +30% は学習リセットに注意</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>ユーザーが8/29に停止済み（Metaで PAUSED を確認）。9日通算で 消化85,838円・21注文・**損益−11,530円**・倍率0.92。CPC 293〜430円は全店平均73〜90円の3〜6倍、link CTR 0.58〜0.65% と、集客段階で構造的に負けていた</t>
+          <t>8/23開始で7日注文32件＝週50CV未達。「学習中の広告セットは予算もCRも触らない」ルールに触れている。採算自体は良い（7日余裕+1.00・倍率1.71・消化率102%）ので止める理由はないが、**増額直後2〜3日は配信ペーシングが追いつかず効率が落ちて見えるのが正常**。単日で慌てて戻さないこと</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>+約8,000円/日</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>完了</t>
+          <t>9/2まで監視</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>🔴 判定日</t>
+          <t>⚠️ 在庫</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド 本判定</t>
+          <t>快適マジックインソール「グリーン」全7サイズが在庫0</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>倍率 ≥1.3 継続 ／ 1.0〜1.3 は−50% ／ &lt;1.0 停止。★増額は日10,000円が上限（3〜5月にリーチを2倍に広げて壊した実測がある）</t>
+          <t>他3色は各1万個以上ある。売れ筋色が買えない状態なので、非表示にするか色の選択肢から落とすかを決める。8/31の増額判定に直接効く</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -2791,34 +3711,34 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>9/1</t>
+          <t>本日</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>🔴 判定日</t>
+          <t>✅ 実行済み</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>決済ミックス 月次再計測</t>
+          <t>3D足臭リセットブラシ 停止</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>直近100注文の paymentGatewayNames × 金額でブレンド率を更新する（現行3.452%）</t>
+          <t>ユーザーが8/29に停止済み（Metaで PAUSED を確認）。9日通算で 消化85,838円・21注文・**損益−11,530円**・倍率0.92。CPC 293〜430円は全店平均73〜90円の3〜6倍、link CTR 0.58〜0.65% と、集客段階で構造的に負けていた</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>+約8,000円/日</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>9/1</t>
+          <t>完了</t>
         </is>
       </c>
     </row>
@@ -2830,12 +3750,12 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>優先配送 790円</t>
+          <t>ナノバブルシャワーヘッド 本判定</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>宣言済み基準「14日で件数 ≥ 28件」。7日実測 **6件**（アタッチ率 6/740 = 0.81%）。前週7件からさらに減少。このペースだと14日で13件前後にしかならず不合格の見込み</t>
+          <t>倍率 ≥1.3 継続 ／ 1.0〜1.3 は−50% ／ &lt;1.0 停止。★増額は日10,000円が上限（3〜5月にリーチを2倍に広げて壊した実測がある）</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -2845,51 +3765,51 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>9/4</t>
+          <t>9/1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>🟡 推奨</t>
+          <t>🔴 判定日</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>アップセル手動ペア5組の設定</t>
+          <t>決済ミックス 月次再計測</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>data/lp/upsell-pairs-2026-08-26.txt の5組をアプリに手入力する。異商品ミックス率が実質ゼロなので自動推薦は学習データがなく全店売れ筋にフォールバックする。判定は実施+14日で異商品ミックス率3.0%以上</t>
+          <t>直近100注文の paymentGatewayNames × 金額でブレンド率を更新する（現行3.452%）</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>週+約4万円</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>9/1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>🟡 推奨</t>
+          <t>🔴 判定日</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>カテゴリタグ40件の付与</t>
+          <t>優先配送 790円</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>data/tags/category-mutation-2026-08-23.graphql を GraphiQL で1回実行 ＋ ナノバブルの季節タグ是正</t>
+          <t>宣言済み基準「14日で件数 ≥ 28件」。7日実測 **6件**（アタッチ率 6/740 = 0.81%）。前週7件からさらに減少。このペースだと14日で13件前後にしかならず不合格の見込み</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -2899,7 +3819,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>任意</t>
+          <t>9/4</t>
         </is>
       </c>
     </row>
@@ -2911,17 +3831,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>コレクション冒頭文7本の貼り付け</t>
+          <t>アップセル手動ペア5組の設定</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>data/lp/collection-intro-2026-08-23.txt。あわせて「暖房・防寒グッズ」コレクションのAmazon由来HTML説明を削除</t>
+          <t>data/lp/upsell-pairs-2026-08-26.txt の5組をアプリに手入力する。異商品ミックス率が実質ゼロなので自動推薦は学習データがなく全店売れ筋にフォールバックする。判定は実施+14日で異商品ミックス率3.0%以上</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>週+約4万円</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -2938,12 +3858,12 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>購入通知アプリ</t>
+          <t>カテゴリタグ40件の付与</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Judge.me の Pop-up Reviews Widget は導入済みアプリの機能なので追加0円。Sales Popを足すならQikify Basic $6.99（訪問者無制限）</t>
+          <t>data/tags/category-mutation-2026-08-23.graphql を GraphiQL で1回実行 ＋ ナノバブルの季節タグ是正</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -2965,20 +3885,74 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
+          <t>コレクション冒頭文7本の貼り付け</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>data/lp/collection-intro-2026-08-23.txt。あわせて「暖房・防寒グッズ」コレクションのAmazon由来HTML説明を削除</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>🟡 推奨</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>購入通知アプリ</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Judge.me の Pop-up Reviews Widget は導入済みアプリの機能なので追加0円。Sales Popを足すならQikify Basic $6.99（訪問者無制限）</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>任意</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>🟡 推奨</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>CJで原価確認</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>あったかインソール 1,000円以下 ／ 外反母趾サポーター 800円以下 なら秋冬のテスト枠に入れる</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>任意</t>
         </is>
@@ -3900,7 +4874,7 @@
         <v>4121</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="X10" s="4" t="inlineStr">
         <is>
@@ -4060,7 +5034,7 @@
         <v>3520</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="X12" s="4" t="inlineStr">
         <is>
@@ -4220,7 +5194,7 @@
         <v>3266</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="X14" s="4" t="inlineStr">
         <is>
@@ -4300,7 +5274,7 @@
         <v>3779</v>
       </c>
       <c r="W15" s="5" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="X15" s="4" t="inlineStr">
         <is>
@@ -4380,7 +5354,7 @@
         <v>4084</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="X16" s="4" t="inlineStr">
         <is>
@@ -4460,7 +5434,7 @@
         <v>3632</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="X17" s="4" t="inlineStr">
         <is>
@@ -5875,10 +6849,10 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>27000</v>
+        <v>30000</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>0.723</v>
+        <v>0.977</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>2.83</v>
@@ -5904,10 +6878,10 @@
         </is>
       </c>
       <c r="L7" s="7" t="n">
-        <v>-29699</v>
+        <v>-32999</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>29699</v>
+        <v>32999</v>
       </c>
       <c r="N7" s="5" t="n">
         <v>213807</v>
@@ -5928,7 +6902,7 @@
         <v>80000</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="E8" s="4" t="n">
         <v>2.01</v>
@@ -5978,7 +6952,7 @@
         <v>35000</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.699</v>
+        <v>0.999</v>
       </c>
       <c r="E9" s="4" t="n">
         <v>2.37</v>
@@ -6016,7 +6990,7 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>ムダ毛シェーバー</t>
+          <t>むくみ取りかっさ</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -6025,48 +6999,46 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>17000</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>0.666</v>
-      </c>
+        <v>13000</v>
+      </c>
+      <c r="D10" s="6" t="inlineStr"/>
       <c r="E10" s="4" t="n">
-        <v>2.73</v>
+        <v>2.41</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1.68</v>
+        <v>1.41</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="I10" s="8" t="n">
-        <v>-0.025</v>
+        <v>0.198</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>0.027</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.299</v>
+        <v>0.369</v>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>⚠️符号が割れる</t>
+          <t>一致</t>
         </is>
       </c>
       <c r="L10" s="7" t="n">
-        <v>-4073</v>
+        <v>-4507</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>4073</v>
+        <v>4507</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>74463</v>
+        <v>43446</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>姿勢サポートチェア</t>
+          <t>ムダ毛シェーバー</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -6075,48 +7047,48 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>0.7</v>
+        <v>0.978</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2.47</v>
+        <v>2.73</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.188</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.019</v>
+        <v>0.137</v>
+      </c>
+      <c r="I11" s="8" t="n">
+        <v>-0.025</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.358</v>
+        <v>0.299</v>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>一致</t>
+          <t>⚠️符号が割れる</t>
         </is>
       </c>
       <c r="L11" s="7" t="n">
-        <v>-3954</v>
+        <v>-4073</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>3954</v>
+        <v>4073</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>58602</v>
+        <v>74463</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>むくみ取りかっさ</t>
+          <t>姿勢サポートチェア</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -6125,26 +7097,28 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D12" s="6" t="inlineStr"/>
+        <v>12000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>1</v>
+      </c>
       <c r="E12" s="4" t="n">
-        <v>2.41</v>
+        <v>2.47</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.198</v>
+        <v>0.188</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.369</v>
+        <v>0.358</v>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
@@ -6152,13 +7126,13 @@
         </is>
       </c>
       <c r="L12" s="7" t="n">
-        <v>-3467</v>
+        <v>-3954</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>3467</v>
+        <v>3954</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>43446</v>
+        <v>58602</v>
       </c>
     </row>
     <row r="13">
@@ -6173,10 +7147,10 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>0.765</v>
+        <v>0.9379999999999999</v>
       </c>
       <c r="E13" s="4" t="n">
         <v>2.29</v>
@@ -6202,10 +7176,10 @@
         </is>
       </c>
       <c r="L13" s="7" t="n">
-        <v>-3194</v>
+        <v>-3833</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>3194</v>
+        <v>3833</v>
       </c>
       <c r="N13" s="5" t="n">
         <v>40092</v>
@@ -6271,10 +7245,10 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.618</v>
+        <v>1.043</v>
       </c>
       <c r="E15" s="4" t="n">
         <v>1.66</v>
@@ -6300,10 +7274,10 @@
         </is>
       </c>
       <c r="L15" s="5" t="n">
-        <v>1342</v>
+        <v>959</v>
       </c>
       <c r="M15" s="7" t="n">
-        <v>-1342</v>
+        <v>-959</v>
       </c>
       <c r="N15" s="5" t="n">
         <v>16315</v>
@@ -6321,10 +7295,10 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>0.697</v>
+        <v>0.996</v>
       </c>
       <c r="E16" s="4" t="n">
         <v>2.07</v>
@@ -6350,10 +7324,10 @@
         </is>
       </c>
       <c r="L16" s="7" t="n">
-        <v>-344</v>
+        <v>-258</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>344</v>
+        <v>258</v>
       </c>
       <c r="N16" s="5" t="n">
         <v>25873</v>
@@ -6419,10 +7393,10 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>0.699</v>
+        <v>0.999</v>
       </c>
       <c r="E18" s="4" t="n">
         <v>2.42</v>
@@ -6448,10 +7422,10 @@
         </is>
       </c>
       <c r="L18" s="7" t="n">
-        <v>-75</v>
+        <v>-63</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="N18" s="5" t="n">
         <v>39370</v>
@@ -9472,7 +10446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9674,12 +10648,12 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>8/31</t>
+          <t>8/31→中止</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>快適マジックインソール 増額判定</t>
+          <t>快適マジックインソール 増額判定（27,000の実験）</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -9689,49 +10663,49 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>P1(8/24-26・予算22,000) 実売193,826 / 52個 / 広告63,511 / 利益+95,111 = **1日31,704円**。P2は8/28-29の2日で 実売117,609 / 31個 / 広告50,062 / 利益+46,560 = **1日23,280円**</t>
+          <t>P1(8/24-26・予算22,000) = 1日31,704円。P2は8/28-29の2日で1日23,280円</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>⚠️ 現時点では基準割れ</t>
+          <t>🚫 執行不能 → 実験を差し替え</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>8/27は22,000→27,000の変更当日なので両窓から除外。8/30の結果次第。★「グリーン」全7サイズ在庫0が効いている可能性があるので、判定時に併記する</t>
+          <t>★8/30 昼に 27,000→30,000 へ再変更されたため、P2窓(8/28-30)の最終日が新予算になり窓が汚染された。SKILL.md「同一キャンペーンの再変更は前の実験を消費する(S1b③)」に従い、この実験は終了させる。参考値としてはP2の2日分が基準割れ（23,280 &lt; 28,310）だが、2日では判定しない</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>9/1</t>
+          <t>9/3</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>ナノバブルシャワーヘッド 本判定</t>
+          <t>快適マジックインソール 増額判定（30,000の実験・新規）</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>倍率 ≥1.3 継続 ／ 1.0〜1.3 は−50% ／ &lt;1.0 停止</t>
+          <t>P2の1日あたり利益 ≥ P1の1日あたり利益</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>7日(8/23-29) MER 2.09・分岐1.48・余裕+0.62</t>
+          <t>P1 = 8/28-29（予算27,000・2日）実売117,609 / 31個 / 広告50,062 / 利益+46,560 = **1日23,280円**。P2 = 8/31-9/2（予算30,000・3日）。8/30は変更当日なので両窓から除外</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>進行中</t>
+          <t>進行中（基準を本日宣言）</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>★増額は日10,000円が上限（3〜5月にリーチを71,205→145,211人へ広げて壊した実測がある）</t>
+          <t>★合格ライン = **1日23,280円以上**。P1が2日しかないので、判定時に「P1が短い」ことを併記する。★「グリーン」全7サイズ在庫0の影響を判定時に必ず併記する</t>
         </is>
       </c>
     </row>
@@ -9743,17 +10717,17 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>決済ミックス 月次再計測</t>
+          <t>ナノバブルシャワーヘッド 本判定</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>直近100注文の paymentGatewayNames × 金額で再計測</t>
+          <t>倍率 ≥1.3 継続 ／ 1.0〜1.3 は−50% ／ &lt;1.0 停止</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>現行 3.452%</t>
+          <t>7日(8/23-29) MER 2.09・分岐1.48・余裕+0.62</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -9763,37 +10737,69 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01実測: SP 76.2%×3.25% ＋ KOMOJUスマホ 16.3%×4.1% ＋ Paidy 7.5%×4.1%</t>
+          <t>★増額は日10,000円が上限（3〜5月にリーチを71,205→145,211人へ広げて壊した実測がある）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>9/1</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>決済ミックス 月次再計測</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>直近100注文の paymentGatewayNames × 金額で再計測</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>現行 3.452%</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>進行中</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-01実測: SP 76.2%×3.25% ＋ KOMOJUスマホ 16.3%×4.1% ＋ Paidy 7.5%×4.1%</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>9/4</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>優先配送 790円</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>14日で件数 ≥ 28件</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>7日実測 **6件**（アタッチ率 6/740 = 0.81%）</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>🚨不合格の見込み</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>前週7件からさらに減少。8/22に536→790へ値上げ済み。14日で13件前後の見込み</t>
         </is>
